--- a/output/yearly_total_coral_cover_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_13_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250841250261942</v>
+        <v>1.254503169198783</v>
       </c>
       <c r="C3" t="n">
-        <v>4.61251273224871</v>
+        <v>4.606818595564079</v>
       </c>
       <c r="D3" t="n">
-        <v>6.150467837715621</v>
+        <v>6.069454017161174</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01382182022627</v>
+        <v>11.93077578192404</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.37008313526653</v>
+        <v>1.380317389864297</v>
       </c>
       <c r="C4" t="n">
-        <v>5.075071689121958</v>
+        <v>5.062167644983205</v>
       </c>
       <c r="D4" t="n">
-        <v>6.468838443673192</v>
+        <v>6.277595668650215</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91399326806168</v>
+        <v>12.72008070349772</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.527770376491927</v>
+        <v>1.552102317460928</v>
       </c>
       <c r="C5" t="n">
-        <v>5.641032269489885</v>
+        <v>5.626230460627811</v>
       </c>
       <c r="D5" t="n">
-        <v>6.936389411616594</v>
+        <v>6.491806371585694</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1051920575984</v>
+        <v>13.67013914967443</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.70079528690349</v>
+        <v>1.752205669082243</v>
       </c>
       <c r="C6" t="n">
-        <v>6.30641022389617</v>
+        <v>6.302563471522942</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3429171225913</v>
+        <v>6.875933755526261</v>
       </c>
       <c r="E6" t="n">
-        <v>15.35012263339096</v>
+        <v>14.93070289613144</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.894586575222755</v>
+        <v>1.973169422755863</v>
       </c>
       <c r="C7" t="n">
-        <v>7.05345872693917</v>
+        <v>7.105855297378746</v>
       </c>
       <c r="D7" t="n">
-        <v>7.76385066243667</v>
+        <v>7.332932642298174</v>
       </c>
       <c r="E7" t="n">
-        <v>16.71189596459859</v>
+        <v>16.41195736243278</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.118130487591026</v>
+        <v>1.206809669918674</v>
       </c>
       <c r="C8" t="n">
-        <v>4.625811985650202</v>
+        <v>4.754083059049885</v>
       </c>
       <c r="D8" t="n">
-        <v>6.065669508180199</v>
+        <v>5.603673225147901</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80961198142143</v>
+        <v>11.56456595411646</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.375742547934595</v>
+        <v>1.517402654459591</v>
       </c>
       <c r="C9" t="n">
-        <v>5.500980001201672</v>
+        <v>5.816268604483978</v>
       </c>
       <c r="D9" t="n">
-        <v>6.645614544051711</v>
+        <v>6.170239598126964</v>
       </c>
       <c r="E9" t="n">
-        <v>13.52233709318798</v>
+        <v>13.50391085707053</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.644668246388487</v>
+        <v>1.851609371737286</v>
       </c>
       <c r="C10" t="n">
-        <v>6.551966238375699</v>
+        <v>7.038640797384283</v>
       </c>
       <c r="D10" t="n">
-        <v>7.203850784434204</v>
+        <v>6.712487692389305</v>
       </c>
       <c r="E10" t="n">
-        <v>15.40048526919839</v>
+        <v>15.60273786151087</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.923203955774357</v>
+        <v>2.206491137570033</v>
       </c>
       <c r="C11" t="n">
-        <v>7.731934121881625</v>
+        <v>8.385301247844723</v>
       </c>
       <c r="D11" t="n">
-        <v>7.801477239814389</v>
+        <v>7.262144940540516</v>
       </c>
       <c r="E11" t="n">
-        <v>17.45661531747037</v>
+        <v>17.85393732595527</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.215723371384422</v>
+        <v>2.561341418092356</v>
       </c>
       <c r="C12" t="n">
-        <v>9.015236481517654</v>
+        <v>9.861371117404166</v>
       </c>
       <c r="D12" t="n">
-        <v>8.391897846640571</v>
+        <v>7.816916908926392</v>
       </c>
       <c r="E12" t="n">
-        <v>19.62285769954265</v>
+        <v>20.23962944442291</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.50341796043883</v>
+        <v>2.90475332018152</v>
       </c>
       <c r="C13" t="n">
-        <v>10.33750586692813</v>
+        <v>11.38686213933713</v>
       </c>
       <c r="D13" t="n">
-        <v>8.937863736910391</v>
+        <v>8.352093641402153</v>
       </c>
       <c r="E13" t="n">
-        <v>21.77878756427734</v>
+        <v>22.64370910092081</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.464011629003971</v>
+        <v>1.674733956243506</v>
       </c>
       <c r="C14" t="n">
-        <v>7.369449872020511</v>
+        <v>8.027211016388833</v>
       </c>
       <c r="D14" t="n">
-        <v>6.739815799378863</v>
+        <v>6.382008031089071</v>
       </c>
       <c r="E14" t="n">
-        <v>15.57327730040335</v>
+        <v>16.08395300372141</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.492325232794449</v>
+        <v>1.720041612794497</v>
       </c>
       <c r="C15" t="n">
-        <v>7.864123087759352</v>
+        <v>8.704018066219541</v>
       </c>
       <c r="D15" t="n">
-        <v>6.810550721469846</v>
+        <v>6.437074259820275</v>
       </c>
       <c r="E15" t="n">
-        <v>16.16699904202365</v>
+        <v>16.86113393883431</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.725932099019978</v>
+        <v>1.991867917146354</v>
       </c>
       <c r="C16" t="n">
-        <v>9.227809918866344</v>
+        <v>10.31451627017418</v>
       </c>
       <c r="D16" t="n">
-        <v>7.327705959635938</v>
+        <v>6.925739179609125</v>
       </c>
       <c r="E16" t="n">
-        <v>18.28144797752226</v>
+        <v>19.23212336692966</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.382664014230081</v>
+        <v>1.594986590227538</v>
       </c>
       <c r="C17" t="n">
-        <v>8.478579340893345</v>
+        <v>9.557480797952421</v>
       </c>
       <c r="D17" t="n">
-        <v>6.843566896763667</v>
+        <v>6.465741292784282</v>
       </c>
       <c r="E17" t="n">
-        <v>16.70481025188709</v>
+        <v>17.61820868096424</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.590558908081385</v>
+        <v>1.820111156288374</v>
       </c>
       <c r="C18" t="n">
-        <v>9.854115866790595</v>
+        <v>11.13307787102108</v>
       </c>
       <c r="D18" t="n">
-        <v>7.299500348092927</v>
+        <v>6.950911190746013</v>
       </c>
       <c r="E18" t="n">
-        <v>18.74417512296491</v>
+        <v>19.90410021805547</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.608819415380376</v>
+        <v>1.829899180899715</v>
       </c>
       <c r="C19" t="n">
-        <v>10.51781658476961</v>
+        <v>11.89358873011588</v>
       </c>
       <c r="D19" t="n">
-        <v>7.431123262801298</v>
+        <v>7.082956256967208</v>
       </c>
       <c r="E19" t="n">
-        <v>19.55775926295128</v>
+        <v>20.8064441679828</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.806995006959637</v>
+        <v>2.048279140232375</v>
       </c>
       <c r="C20" t="n">
-        <v>12.11035862321357</v>
+        <v>13.67518592396665</v>
       </c>
       <c r="D20" t="n">
-        <v>7.944842384002526</v>
+        <v>7.561332460815551</v>
       </c>
       <c r="E20" t="n">
-        <v>21.86219601417573</v>
+        <v>23.28479752501457</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.088699299147458</v>
+        <v>1.223699425958437</v>
       </c>
       <c r="C21" t="n">
-        <v>8.93722241588633</v>
+        <v>10.03350080731057</v>
       </c>
       <c r="D21" t="n">
-        <v>6.625029857798325</v>
+        <v>6.326205491579682</v>
       </c>
       <c r="E21" t="n">
-        <v>16.65095157283211</v>
+        <v>17.58340572484869</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_13_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254503169198783</v>
+        <v>1.264909694863799</v>
       </c>
       <c r="C3" t="n">
-        <v>4.606818595564079</v>
+        <v>4.642171330394007</v>
       </c>
       <c r="D3" t="n">
-        <v>6.069454017161174</v>
+        <v>6.07150586986305</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93077578192404</v>
+        <v>11.97858689512086</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380317389864297</v>
+        <v>1.405088485397005</v>
       </c>
       <c r="C4" t="n">
-        <v>5.062167644983205</v>
+        <v>5.176782943450373</v>
       </c>
       <c r="D4" t="n">
-        <v>6.277595668650215</v>
+        <v>6.373923786741208</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72008070349772</v>
+        <v>12.95579521558859</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.552102317460928</v>
+        <v>1.587400725096989</v>
       </c>
       <c r="C5" t="n">
-        <v>5.626230460627811</v>
+        <v>5.861566456045876</v>
       </c>
       <c r="D5" t="n">
-        <v>6.491806371585694</v>
+        <v>6.700985735102634</v>
       </c>
       <c r="E5" t="n">
-        <v>13.67013914967443</v>
+        <v>14.1499529162455</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.752205669082243</v>
+        <v>1.798076623246831</v>
       </c>
       <c r="C6" t="n">
-        <v>6.302563471522942</v>
+        <v>6.704164058134159</v>
       </c>
       <c r="D6" t="n">
-        <v>6.875933755526261</v>
+        <v>7.034469163584157</v>
       </c>
       <c r="E6" t="n">
-        <v>14.93070289613144</v>
+        <v>15.53670984496515</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.973169422755863</v>
+        <v>2.036243851016597</v>
       </c>
       <c r="C7" t="n">
-        <v>7.105855297378746</v>
+        <v>7.759207490085556</v>
       </c>
       <c r="D7" t="n">
-        <v>7.332932642298174</v>
+        <v>7.504123062142839</v>
       </c>
       <c r="E7" t="n">
-        <v>16.41195736243278</v>
+        <v>17.29957440324499</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.206809669918674</v>
+        <v>1.248866083103034</v>
       </c>
       <c r="C8" t="n">
-        <v>4.754083059049885</v>
+        <v>5.463313194039632</v>
       </c>
       <c r="D8" t="n">
-        <v>5.603673225147901</v>
+        <v>5.742812071116767</v>
       </c>
       <c r="E8" t="n">
-        <v>11.56456595411646</v>
+        <v>12.45499134825943</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.517402654459591</v>
+        <v>1.564881146817413</v>
       </c>
       <c r="C9" t="n">
-        <v>5.816268604483978</v>
+        <v>6.786787802199256</v>
       </c>
       <c r="D9" t="n">
-        <v>6.170239598126964</v>
+        <v>6.250663574747233</v>
       </c>
       <c r="E9" t="n">
-        <v>13.50391085707053</v>
+        <v>14.6023325237639</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.851609371737286</v>
+        <v>1.889052192867583</v>
       </c>
       <c r="C10" t="n">
-        <v>7.038640797384283</v>
+        <v>8.248939801815565</v>
       </c>
       <c r="D10" t="n">
-        <v>6.712487692389305</v>
+        <v>6.789018459265814</v>
       </c>
       <c r="E10" t="n">
-        <v>15.60273786151087</v>
+        <v>16.92701045394896</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.206491137570033</v>
+        <v>2.222259596110851</v>
       </c>
       <c r="C11" t="n">
-        <v>8.385301247844723</v>
+        <v>9.779135941674381</v>
       </c>
       <c r="D11" t="n">
-        <v>7.262144940540516</v>
+        <v>7.351979708093817</v>
       </c>
       <c r="E11" t="n">
-        <v>17.85393732595527</v>
+        <v>19.35337524587905</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.561341418092356</v>
+        <v>2.538068788092017</v>
       </c>
       <c r="C12" t="n">
-        <v>9.861371117404166</v>
+        <v>11.34922690396964</v>
       </c>
       <c r="D12" t="n">
-        <v>7.816916908926392</v>
+        <v>7.916265027242322</v>
       </c>
       <c r="E12" t="n">
-        <v>20.23962944442291</v>
+        <v>21.80356071930398</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.90475332018152</v>
+        <v>2.832042608194299</v>
       </c>
       <c r="C13" t="n">
-        <v>11.38686213933713</v>
+        <v>12.9152703222448</v>
       </c>
       <c r="D13" t="n">
-        <v>8.352093641402153</v>
+        <v>8.376297076626079</v>
       </c>
       <c r="E13" t="n">
-        <v>22.64370910092081</v>
+        <v>24.12361000706518</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.674733956243506</v>
+        <v>1.625892007957228</v>
       </c>
       <c r="C14" t="n">
-        <v>8.027211016388833</v>
+        <v>8.972850040073446</v>
       </c>
       <c r="D14" t="n">
-        <v>6.382008031089071</v>
+        <v>6.373712262988184</v>
       </c>
       <c r="E14" t="n">
-        <v>16.08395300372141</v>
+        <v>16.97245431101886</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.720041612794497</v>
+        <v>1.647254838001638</v>
       </c>
       <c r="C15" t="n">
-        <v>8.704018066219541</v>
+        <v>9.594266884430549</v>
       </c>
       <c r="D15" t="n">
-        <v>6.437074259820275</v>
+        <v>6.419903492472997</v>
       </c>
       <c r="E15" t="n">
-        <v>16.86113393883431</v>
+        <v>17.66142521490519</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.991867917146354</v>
+        <v>1.892907748558275</v>
       </c>
       <c r="C16" t="n">
-        <v>10.31451627017418</v>
+        <v>11.23532689441839</v>
       </c>
       <c r="D16" t="n">
-        <v>6.925739179609125</v>
+        <v>6.971527892535194</v>
       </c>
       <c r="E16" t="n">
-        <v>19.23212336692966</v>
+        <v>20.09976253551186</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.594986590227538</v>
+        <v>1.503890220750477</v>
       </c>
       <c r="C17" t="n">
-        <v>9.557480797952421</v>
+        <v>10.24067902533778</v>
       </c>
       <c r="D17" t="n">
-        <v>6.465741292784282</v>
+        <v>6.505727876778253</v>
       </c>
       <c r="E17" t="n">
-        <v>17.61820868096424</v>
+        <v>18.25029712286651</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.820111156288374</v>
+        <v>1.703410806684556</v>
       </c>
       <c r="C18" t="n">
-        <v>11.13307787102108</v>
+        <v>11.88048239826418</v>
       </c>
       <c r="D18" t="n">
-        <v>6.950911190746013</v>
+        <v>6.989758947403058</v>
       </c>
       <c r="E18" t="n">
-        <v>19.90410021805547</v>
+        <v>20.5736521523518</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.829899180899715</v>
+        <v>1.699513268298696</v>
       </c>
       <c r="C19" t="n">
-        <v>11.89358873011588</v>
+        <v>12.63800874433806</v>
       </c>
       <c r="D19" t="n">
-        <v>7.082956256967208</v>
+        <v>7.110317565484566</v>
       </c>
       <c r="E19" t="n">
-        <v>20.8064441679828</v>
+        <v>21.44783957812133</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.048279140232375</v>
+        <v>1.888342621733528</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67518592396665</v>
+        <v>14.52970894322011</v>
       </c>
       <c r="D20" t="n">
-        <v>7.561332460815551</v>
+        <v>7.564218799066037</v>
       </c>
       <c r="E20" t="n">
-        <v>23.28479752501457</v>
+        <v>23.98227036401968</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.223699425958437</v>
+        <v>1.119820701372082</v>
       </c>
       <c r="C21" t="n">
-        <v>10.03350080731057</v>
+        <v>10.69793783606777</v>
       </c>
       <c r="D21" t="n">
-        <v>6.326205491579682</v>
+        <v>6.337888289260219</v>
       </c>
       <c r="E21" t="n">
-        <v>17.58340572484869</v>
+        <v>18.15564682670007</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_13_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264909694863799</v>
+        <v>2.592530136919209</v>
       </c>
       <c r="C3" t="n">
-        <v>4.642171330394007</v>
+        <v>7.763127870779989</v>
       </c>
       <c r="D3" t="n">
-        <v>6.07150586986305</v>
+        <v>8.189629161636848</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97858689512086</v>
+        <v>18.54528716933605</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.405088485397005</v>
+        <v>1.061922006079055</v>
       </c>
       <c r="C4" t="n">
-        <v>5.176782943450373</v>
+        <v>4.609279634480998</v>
       </c>
       <c r="D4" t="n">
-        <v>6.373923786741208</v>
+        <v>5.838237277115941</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95579521558859</v>
+        <v>11.50943891767599</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.587400725096989</v>
+        <v>1.145141604328527</v>
       </c>
       <c r="C5" t="n">
-        <v>5.861566456045876</v>
+        <v>5.351504582732706</v>
       </c>
       <c r="D5" t="n">
-        <v>6.700985735102634</v>
+        <v>6.122962541075725</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1499529162455</v>
+        <v>12.61960872813696</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.798076623246831</v>
+        <v>1.234916336482083</v>
       </c>
       <c r="C6" t="n">
-        <v>6.704164058134159</v>
+        <v>6.274089841831419</v>
       </c>
       <c r="D6" t="n">
-        <v>7.034469163584157</v>
+        <v>6.472290441928465</v>
       </c>
       <c r="E6" t="n">
-        <v>15.53670984496515</v>
+        <v>13.98129662024197</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.036243851016597</v>
+        <v>1.333596561415758</v>
       </c>
       <c r="C7" t="n">
-        <v>7.759207490085556</v>
+        <v>7.331267949775449</v>
       </c>
       <c r="D7" t="n">
-        <v>7.504123062142839</v>
+        <v>6.859668655151724</v>
       </c>
       <c r="E7" t="n">
-        <v>17.29957440324499</v>
+        <v>15.52453316634293</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.248866083103034</v>
+        <v>1.433808788690545</v>
       </c>
       <c r="C8" t="n">
-        <v>5.463313194039632</v>
+        <v>8.514718672174558</v>
       </c>
       <c r="D8" t="n">
-        <v>5.742812071116767</v>
+        <v>7.268512865944937</v>
       </c>
       <c r="E8" t="n">
-        <v>12.45499134825943</v>
+        <v>17.21704032681004</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.564881146817413</v>
+        <v>1.519817900250698</v>
       </c>
       <c r="C9" t="n">
-        <v>6.786787802199256</v>
+        <v>9.825516935739</v>
       </c>
       <c r="D9" t="n">
-        <v>6.250663574747233</v>
+        <v>7.715907792875004</v>
       </c>
       <c r="E9" t="n">
-        <v>14.6023325237639</v>
+        <v>19.0612426288647</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.889052192867583</v>
+        <v>0.9624367269042756</v>
       </c>
       <c r="C10" t="n">
-        <v>8.248939801815565</v>
+        <v>7.169212610262333</v>
       </c>
       <c r="D10" t="n">
-        <v>6.789018459265814</v>
+        <v>6.080503493637831</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92701045394896</v>
+        <v>14.21215283080444</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.222259596110851</v>
+        <v>0.8790470769055515</v>
       </c>
       <c r="C11" t="n">
-        <v>9.779135941674381</v>
+        <v>7.621435055269541</v>
       </c>
       <c r="D11" t="n">
-        <v>7.351979708093817</v>
+        <v>5.95344570575421</v>
       </c>
       <c r="E11" t="n">
-        <v>19.35337524587905</v>
+        <v>14.4539278379293</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.538068788092017</v>
+        <v>0.9229802866705963</v>
       </c>
       <c r="C12" t="n">
-        <v>11.34922690396964</v>
+        <v>9.030370638065266</v>
       </c>
       <c r="D12" t="n">
-        <v>7.916265027242322</v>
+        <v>6.401642985174007</v>
       </c>
       <c r="E12" t="n">
-        <v>21.80356071930398</v>
+        <v>16.35499390990987</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.832042608194299</v>
+        <v>0.7127488332831844</v>
       </c>
       <c r="C13" t="n">
-        <v>12.9152703222448</v>
+        <v>8.600983644658839</v>
       </c>
       <c r="D13" t="n">
-        <v>8.376297076626079</v>
+        <v>5.865608738655248</v>
       </c>
       <c r="E13" t="n">
-        <v>24.12361000706518</v>
+        <v>15.17934121659727</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.625892007957228</v>
+        <v>0.7519205666826321</v>
       </c>
       <c r="C14" t="n">
-        <v>8.972850040073446</v>
+        <v>10.11935464404696</v>
       </c>
       <c r="D14" t="n">
-        <v>6.373712262988184</v>
+        <v>6.275871286782947</v>
       </c>
       <c r="E14" t="n">
-        <v>16.97245431101886</v>
+        <v>17.14714649751254</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.647254838001638</v>
+        <v>0.7122088720458485</v>
       </c>
       <c r="C15" t="n">
-        <v>9.594266884430549</v>
+        <v>10.98288028974837</v>
       </c>
       <c r="D15" t="n">
-        <v>6.419903492472997</v>
+        <v>6.37289741239366</v>
       </c>
       <c r="E15" t="n">
-        <v>17.66142521490519</v>
+        <v>18.06798657418787</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.892907748558275</v>
+        <v>0.7638193488581034</v>
       </c>
       <c r="C16" t="n">
-        <v>11.23532689441839</v>
+        <v>12.90257011567849</v>
       </c>
       <c r="D16" t="n">
-        <v>6.971527892535194</v>
+        <v>6.890239182623559</v>
       </c>
       <c r="E16" t="n">
-        <v>20.09976253551186</v>
+        <v>20.55662864716016</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.503890220750477</v>
+        <v>0.4555407522475625</v>
       </c>
       <c r="C17" t="n">
-        <v>10.24067902533778</v>
+        <v>9.763598728459041</v>
       </c>
       <c r="D17" t="n">
-        <v>6.505727876778253</v>
+        <v>5.769063669419617</v>
       </c>
       <c r="E17" t="n">
-        <v>18.25029712286651</v>
+        <v>15.98820315012622</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.703410806684556</v>
+        <v>0.3384084336538755</v>
       </c>
       <c r="C18" t="n">
-        <v>11.88048239826418</v>
+        <v>8.845311195814743</v>
       </c>
       <c r="D18" t="n">
-        <v>6.989758947403058</v>
+        <v>5.331881599241471</v>
       </c>
       <c r="E18" t="n">
-        <v>20.5736521523518</v>
+        <v>14.51560122871009</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.699513268298696</v>
+        <v>0.3850414496055991</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63800874433806</v>
+        <v>11.0356197764205</v>
       </c>
       <c r="D19" t="n">
-        <v>7.110317565484566</v>
+        <v>5.847632938190489</v>
       </c>
       <c r="E19" t="n">
-        <v>21.44783957812133</v>
+        <v>17.26829416421659</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.888342621733528</v>
+        <v>0.427236965934127</v>
       </c>
       <c r="C20" t="n">
-        <v>14.52970894322011</v>
+        <v>13.32565428882365</v>
       </c>
       <c r="D20" t="n">
-        <v>7.564218799066037</v>
+        <v>6.390853577904335</v>
       </c>
       <c r="E20" t="n">
-        <v>23.98227036401968</v>
+        <v>20.14374483266212</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.119820701372082</v>
+        <v>0.4649557127312894</v>
       </c>
       <c r="C21" t="n">
-        <v>10.69793783606777</v>
+        <v>15.58048332855252</v>
       </c>
       <c r="D21" t="n">
-        <v>6.337888289260219</v>
+        <v>6.917482681416407</v>
       </c>
       <c r="E21" t="n">
-        <v>18.15564682670007</v>
+        <v>22.96292172270022</v>
       </c>
     </row>
   </sheetData>
